--- a/fhir/core/StructureDefinition-dk-core-x-ecpr-identifier.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-x-ecpr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.5.0</t>
+    <t>3.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T17:27:08+01:00</t>
+    <t>2026-03-11T23:16:27+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -459,7 +459,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-x-ecpr:Requirement of danish X-eCPR. See https://www.nspop.dk/pages/viewpage.action?pageId=226757583#eCPRFormater(XeCPRogDeCPR)-Formatetfornationaleerstatningspersonnumre-X-eCPR {value.matches('^((((0[1-9]|1[0-9]|2[0-9]|3[0-1])(01|03|05|07|08|10|12))|((0[1-9]|1[0-9]|2[0-9]|30)(04|06|09|11))|((0[1-9]|1[0-9]|2[0-9])(02)))([0-9]{2})((1|7){1})([A-Z]{2})([0-9]{1}))$')}</t>
+x-ecpr:Requirement of danish X-eCPR. See https://www.nspop.dk/pages/viewpage.action?pageId=226757583#eCPRFormater(XeCPRogDeCPR)-Formatetfornationaleerstatningspersonnumre-X-eCPR {matches('^((((0[1-9]|1[0-9]|2[0-9]|3[0-1])(01|03|05|07|08|10|12))|((0[1-9]|1[0-9]|2[0-9]|30)(04|06|09|11))|((0[1-9]|1[0-9]|2[0-9])(02)))([0-9]{2})((1|7){1})([A-Z]{2})([0-9]{1}))$')}</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>

--- a/fhir/core/StructureDefinition-dk-core-x-ecpr-identifier.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-x-ecpr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.6.0</t>
+    <t>3.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T23:16:27+01:00</t>
+    <t>2026-05-30T15:25:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
